--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2111,7 +2111,13 @@
         <v>tabela regressiva ir</v>
       </c>
       <c r="D100" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F100" s="1" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="G100" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=rNlibeZsKfI | Short: https://www.youtube.com/watch?v=MQWeTL_TVLY</v>
       </c>
       <c r="I100" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2253,7 +2253,13 @@
         <v>portabilidade salario</v>
       </c>
       <c r="D108" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F108" s="1" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="G108" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=59iVvf9K6OY | Short: https://www.youtube.com/watch?v=06kggW_oIwU</v>
       </c>
       <c r="I108" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4679,7 +4679,13 @@
         <v>aluguel maquininha</v>
       </c>
       <c r="D250" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F250" s="1" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="G250" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=hSExCJPBdMg | Short: https://www.youtube.com/watch?v=HxjHbzbSFLc</v>
       </c>
       <c r="I250" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2565,7 +2565,13 @@
         <v>saldo devedor</v>
       </c>
       <c r="D126" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F126" s="1" t="str">
+        <v>30/06/2026</v>
+      </c>
+      <c r="G126" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Nxi_6CQkN6o | Short: https://www.youtube.com/watch?v=Cy7UWwUvaMU</v>
       </c>
       <c r="I126" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4039,7 +4039,13 @@
         <v>renda fixa selic alta</v>
       </c>
       <c r="D212" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F212" s="1" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G212" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=iLTdnHhqiyU | Short: https://www.youtube.com/watch?v=Cn28JylzcBE</v>
       </c>
       <c r="I212" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2690,7 +2690,13 @@
         <v>score interno banco</v>
       </c>
       <c r="D133" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F133" s="1" t="str">
+        <v>02/07/2026</v>
+      </c>
+      <c r="G133" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=B0xwOs5DiH0 | Short: https://www.youtube.com/watch?v=PLLC8vObUCA</v>
       </c>
       <c r="I133" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5230,7 +5230,13 @@
         <v>titulo capitalizacao vale</v>
       </c>
       <c r="D281" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F281" s="1" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="G281" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=DirSyBlCjMQ | Short: https://www.youtube.com/watch?v=1FkM7U6Baro</v>
       </c>
       <c r="I281" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -853,7 +853,13 @@
         <v>milhas aereas</v>
       </c>
       <c r="D26" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <v>04/07/2026</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vmgNQjvFDs4 | Short: https://www.youtube.com/watch?v=z2HKUU9faeo</v>
       </c>
       <c r="I26" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4000,7 +4000,13 @@
         <v>orcamento natal</v>
       </c>
       <c r="D209" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F209" s="1" t="str">
+        <v>05/07/2026</v>
+      </c>
+      <c r="G209" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=RXRNnCCpQQM | Short: https://www.youtube.com/watch?v=u007W4JePOc</v>
       </c>
       <c r="I209" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1267,7 +1267,13 @@
         <v>financiamento estudantil</v>
       </c>
       <c r="D50" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F50" s="1" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="G50" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=J13kqL_7BKE | Short: https://www.youtube.com/watch?v=cwHLT38hwUk</v>
       </c>
       <c r="I50" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -700,7 +700,13 @@
         <v>cheque especial</v>
       </c>
       <c r="D17" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=b4u8nKN4wds | Short: https://www.youtube.com/watch?v=16vu7QdrK1I</v>
       </c>
       <c r="I17" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5447,7 +5447,13 @@
         <v>tarifas abrir conta</v>
       </c>
       <c r="D292" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F292" s="1" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="G292" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=UhTwNXtPoz8 | Short: https://www.youtube.com/watch?v=YmwA3pWCWLw</v>
       </c>
       <c r="I292" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1432,7 +1432,13 @@
         <v>antecipacao recebiveis</v>
       </c>
       <c r="D59" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F59" s="1" t="str">
+        <v>11/07/2026</v>
+      </c>
+      <c r="G59" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=bGYdl7h0d_w | Short: https://www.youtube.com/watch?v=T_NV9Wp8EKY</v>
       </c>
       <c r="I59" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4200,7 +4200,13 @@
         <v>pagar a si mesmo</v>
       </c>
       <c r="D219" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F219" s="1" t="str">
+        <v>12/07/2026</v>
+      </c>
+      <c r="G219" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=GiSSMvuDtiM | Short: https://www.youtube.com/watch?v=a5W9-28CdTc</v>
       </c>
       <c r="I219" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -615,7 +615,13 @@
         <v>parcelamento fatura</v>
       </c>
       <c r="D12" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=uy159XBzdR8 | Short: https://www.youtube.com/watch?v=eERkdS6hnT0</v>
       </c>
       <c r="I12" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3939,7 +3939,13 @@
         <v>priorizar dividas</v>
       </c>
       <c r="D204" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F204" s="1" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="G204" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=R-P_Tg_0udI | Short: https://www.youtube.com/watch?v=MR1c6_0z6Qk</v>
       </c>
       <c r="I204" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1336,7 +1336,13 @@
         <v>seguro viagem</v>
       </c>
       <c r="D53" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F53" s="1" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="G53" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=r5L4gdzpqnU | Short: https://www.youtube.com/watch?v=HfCf5oGJZV0</v>
       </c>
       <c r="I53" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5216,7 +5216,13 @@
         <v>ciclo de emprestimo</v>
       </c>
       <c r="D277" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F277" s="1" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G277" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=iFp_nwnzMMs | Short: https://www.youtube.com/watch?v=KLPTid8j_xg</v>
       </c>
       <c r="I277" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5466,7 +5466,13 @@
         <v>renda passiva garantida</v>
       </c>
       <c r="D291" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F291" s="1" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="G291" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=fEtS-El1NuM | Short: https://www.youtube.com/watch?v=RSnzP_mMR4I</v>
       </c>
       <c r="I291" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5080,7 +5080,13 @@
         <v>tarifas conta pj</v>
       </c>
       <c r="D269" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F269" s="1" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="G269" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=1f-eL3Bk8QI | Short: https://www.youtube.com/watch?v=BSasCllEKIM</v>
       </c>
       <c r="I269" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -939,7 +939,13 @@
         <v>conta digital rendimento</v>
       </c>
       <c r="D30" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <v>18/07/2026</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xbm2uXV_31I | Short: https://www.youtube.com/watch?v=WZeqcx5e8G8</v>
       </c>
       <c r="I30" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2539,7 +2539,13 @@
         <v>anuidade cartao</v>
       </c>
       <c r="D122" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F122" s="1" t="str">
+        <v>19/07/2026</v>
+      </c>
+      <c r="G122" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=XoJB3Wki-xA | Short: https://www.youtube.com/watch?v=j2tnnvKgYtk</v>
       </c>
       <c r="I122" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2034,7 +2034,13 @@
         <v>negativacao nome</v>
       </c>
       <c r="D93" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F93" s="1" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="G93" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=PTixPaMnrwM | Short: https://www.youtube.com/watch?v=cbN-ziRHXyI</v>
       </c>
       <c r="I93" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4276,7 +4276,13 @@
         <v>economizar farmacia</v>
       </c>
       <c r="D221" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F221" s="1" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="G221" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=iSKTvlMVzzc | Short: https://www.youtube.com/watch?v=-Wny64E3kpU</v>
       </c>
       <c r="I221" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4469,7 +4469,13 @@
         <v>recusar produto banco</v>
       </c>
       <c r="D232" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F232" s="1" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G232" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=NwOJRqY5amo | Short: https://www.youtube.com/watch?v=EOuhp2qDqGM</v>
       </c>
       <c r="I232" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1013,7 +1013,13 @@
         <v>leasing veiculo</v>
       </c>
       <c r="D34" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F34" s="1" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=jp_DxVW04ak | Short: https://www.youtube.com/watch?v=FIKMh8FCcvc</v>
       </c>
       <c r="I34" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4441,7 +4441,13 @@
         <v>identificar piramide</v>
       </c>
       <c r="D230" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F230" s="1" t="str">
+        <v>24/07/2026</v>
+      </c>
+      <c r="G230" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=uVIdxzNjDAI | Short: https://www.youtube.com/watch?v=3lpLi_VQzg8</v>
       </c>
       <c r="I230" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3289,7 +3289,13 @@
         <v>renda extra clt</v>
       </c>
       <c r="D164" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F164" s="1" t="str">
+        <v>25/07/2026</v>
+      </c>
+      <c r="G164" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=1rXUifxMUHE | Short: https://www.youtube.com/watch?v=XFjs3pP1boU</v>
       </c>
       <c r="I164" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2807,7 +2807,13 @@
         <v>desconto a vista</v>
       </c>
       <c r="D136" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F136" s="1" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="G136" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=8DKV9ceqCTk | Short: https://www.youtube.com/watch?v=_P7c1fpReCc</v>
       </c>
       <c r="I136" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3692,7 +3692,13 @@
         <v>planejamento financeiro anual</v>
       </c>
       <c r="D187" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F187" s="1" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="G187" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=QnusYNjQwmA | Short: https://www.youtube.com/watch?v=Hk-go1RfpHY</v>
       </c>
       <c r="I187" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2239,7 +2239,13 @@
         <v>igpm ipca aluguel</v>
       </c>
       <c r="D104" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F104" s="1" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="G104" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=yYq36bW5ZnE | Short: https://www.youtube.com/watch?v=RDPH6jz7CMo</v>
       </c>
       <c r="I104" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3908,7 +3908,13 @@
         <v>planilha de gastos</v>
       </c>
       <c r="D199" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F199" s="1" t="str">
+        <v>29/07/2026</v>
+      </c>
+      <c r="G199" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ChkmFg0pRsg | Short: https://www.youtube.com/watch?v=70hEEicz_0E</v>
       </c>
       <c r="I199" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3647,7 +3647,13 @@
         <v>fundo de emergencia</v>
       </c>
       <c r="D184" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F184" s="1" t="str">
+        <v>30/07/2026</v>
+      </c>
+      <c r="G184" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ouC-JMa4MYo | Short: https://www.youtube.com/watch?v=yUdZCr7DO5Y</v>
       </c>
       <c r="I184" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4392,7 +4392,13 @@
         <v>comprar sem financiamento</v>
       </c>
       <c r="D225" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F225" s="1" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="G225" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=RsPHh3tzl9A | Short: https://www.youtube.com/watch?v=bx-KXRi_jt0</v>
       </c>
       <c r="I225" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3006,7 +3006,13 @@
         <v>pagamento minimo banco</v>
       </c>
       <c r="D147" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F147" s="1" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="G147" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=4AumXplrLs4 | Short: https://www.youtube.com/watch?v=N9Lq9dTHD9U</v>
       </c>
       <c r="I147" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5528,7 +5528,13 @@
         <v>armadilha cashback</v>
       </c>
       <c r="D289" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F289" s="1" t="str">
+        <v>02/08/2026</v>
+      </c>
+      <c r="G289" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Zuf_OoXkdBg | Short: https://www.youtube.com/watch?v=ki0nSLK4QnI</v>
       </c>
       <c r="I289" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5136,7 +5136,13 @@
         <v>cet renegociacao</v>
       </c>
       <c r="D267" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F267" s="1" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="G267" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=CEGoRTqHWMw | Short: https://www.youtube.com/watch?v=ieyiJ7xQbxU</v>
       </c>
       <c r="I267" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4142,7 +4142,13 @@
         <v>quitar ou investir</v>
       </c>
       <c r="D211" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F211" s="1" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="G211" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=D8O-sfwmzwg | Short: https://www.youtube.com/watch?v=wo6dKOKvTh4</v>
       </c>
       <c r="I211" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1785,7 +1785,13 @@
         <v>serasa score</v>
       </c>
       <c r="D78" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F78" s="1" t="str">
+        <v>05/08/2026</v>
+      </c>
+      <c r="G78" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vTPdnb_4dgs | Short: https://www.youtube.com/watch?v=rJRWeQXGJZg</v>
       </c>
       <c r="I78" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1808,7 +1808,13 @@
         <v>birôs de credito</v>
       </c>
       <c r="D79" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F79" s="1" t="str">
+        <v>06/08/2026</v>
+      </c>
+      <c r="G79" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=WXrsamSxutE | Short: https://www.youtube.com/watch?v=VDNuQ8xfgzs</v>
       </c>
       <c r="I79" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4456,7 +4456,13 @@
         <v>perguntas antes de assinar</v>
       </c>
       <c r="D227" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F227" s="1" t="str">
+        <v>07/08/2026</v>
+      </c>
+      <c r="G227" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=f7ZNeaQS4PU | Short: https://www.youtube.com/watch?v=Iw1Zqx0ThLg</v>
       </c>
       <c r="I227" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1984,7 +1984,13 @@
         <v>iof</v>
       </c>
       <c r="D89" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F89" s="1" t="str">
+        <v>08/08/2026</v>
+      </c>
+      <c r="G89" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Qv1ZuAVogdc | Short: https://www.youtube.com/watch?v=xim9e_RDRwI</v>
       </c>
       <c r="I89" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2871,7 +2871,13 @@
         <v>fundo comum consorcio</v>
       </c>
       <c r="D138" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F138" s="1" t="str">
+        <v>09/08/2026</v>
+      </c>
+      <c r="G138" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=9gDn9FdG_Cs | Short: https://www.youtube.com/watch?v=ihCTxdPA10g</v>
       </c>
       <c r="I138" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1036,7 +1036,13 @@
         <v>plano funerario</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F35" s="1" t="str">
+        <v>11/08/2026</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=VWrqonujFdg | Short: https://www.youtube.com/watch?v=oasHbdTm6Ic</v>
       </c>
       <c r="I35" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4940,7 +4940,13 @@
         <v>estorno produto</v>
       </c>
       <c r="D253" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F253" s="1" t="str">
+        <v>12/08/2026</v>
+      </c>
+      <c r="G253" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=a0R-mUnwSNU | Short: https://www.youtube.com/watch?v=AlrRbiI0chU</v>
       </c>
       <c r="I253" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -888,7 +888,13 @@
         <v>previdencia privada</v>
       </c>
       <c r="D27" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <v>13/08/2026</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=3yiG329QYTg | Short: https://www.youtube.com/watch?v=tOaGQwlp500</v>
       </c>
       <c r="I27" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2366,7 +2366,13 @@
         <v>consignado folha</v>
       </c>
       <c r="D109" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F109" s="1" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="G109" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=mLeyqraJrR8 | Short: https://www.youtube.com/watch?v=CO2QABvTYWg</v>
       </c>
       <c r="I109" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4230,7 +4230,13 @@
         <v>rendimento diario</v>
       </c>
       <c r="D213" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F213" s="1" t="str">
+        <v>15/08/2026</v>
+      </c>
+      <c r="G213" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=SmvJN3gTNLM | Short: https://www.youtube.com/watch?v=nmAwEmyraWU</v>
       </c>
       <c r="I213" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3843,7 +3843,13 @@
         <v>comprar tesouro direto</v>
       </c>
       <c r="D192" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F192" s="1" t="str">
+        <v>16/08/2026</v>
+      </c>
+      <c r="G192" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=j9J44tB7VC8 | Short: https://www.youtube.com/watch?v=oyfhoDBpwdw</v>
       </c>
       <c r="I192" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5521,7 +5521,13 @@
         <v>lance consorcio furada</v>
       </c>
       <c r="D284" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F284" s="1" t="str">
+        <v>17/08/2026</v>
+      </c>
+      <c r="G284" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=9pl3KgFu5gE | Short: https://www.youtube.com/watch?v=RWGLQ0zknvk</v>
       </c>
       <c r="I284" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -831,7 +831,13 @@
         <v>cashback</v>
       </c>
       <c r="D24" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F24" s="1" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=eKSAyshTfOs | Short: https://www.youtube.com/watch?v=PUmswqb-YJQ</v>
       </c>
       <c r="I24" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5823,7 +5823,13 @@
         <v>consultor que vende</v>
       </c>
       <c r="D300" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F300" s="1" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="G300" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xZbsVYztoAw | Short: https://www.youtube.com/watch?v=Rm1MV5bpTKA</v>
       </c>
       <c r="I300" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1769,7 +1769,13 @@
         <v>conta salario</v>
       </c>
       <c r="D76" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F76" s="1" t="str">
+        <v>20/08/2026</v>
+      </c>
+      <c r="G76" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=TB3Kz3yJUzE | Short: https://www.youtube.com/watch?v=yuPDVxHONps</v>
       </c>
       <c r="I76" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2992,7 +2992,13 @@
         <v>credito mei</v>
       </c>
       <c r="D143" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F143" s="1" t="str">
+        <v>22/08/2026</v>
+      </c>
+      <c r="G143" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Spz5WJi2T5g | Short: https://www.youtube.com/watch?v=zoJN_zjSCGE</v>
       </c>
       <c r="I143" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1531,7 +1531,13 @@
         <v>financiamento moveis</v>
       </c>
       <c r="D62" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F62" s="1" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="G62" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=QekYYdpfeSY | Short: https://www.youtube.com/watch?v=bOagQNl8TbY</v>
       </c>
       <c r="I62" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5045,7 +5045,13 @@
         <v>parcelado sem juros</v>
       </c>
       <c r="D256" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F256" s="1" t="str">
+        <v>05/09/2026</v>
+      </c>
+      <c r="G256" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=-JDDs1OxKRc | Short: https://www.youtube.com/watch?v=Pfs05zUTIK4</v>
       </c>
       <c r="I256" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2236,7 +2236,13 @@
         <v>tesouro direto marcacao</v>
       </c>
       <c r="D101" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F101" s="1" t="str">
+        <v>06/09/2026</v>
+      </c>
+      <c r="G101" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ZDmCUMR3VJA | Short: https://www.youtube.com/watch?v=jWX1iBmWGPA</v>
       </c>
       <c r="I101" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3277,7 +3277,13 @@
         <v>quitar dividas metodo</v>
       </c>
       <c r="D158" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F158" s="1" t="str">
+        <v>07/09/2026</v>
+      </c>
+      <c r="G158" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=GDslfc5gWug | Short: https://www.youtube.com/watch?v=qixmvHzi23g</v>
       </c>
       <c r="I158" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3862,7 +3862,13 @@
         <v>sair da poupanca</v>
       </c>
       <c r="D191" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F191" s="1" t="str">
+        <v>08/09/2026</v>
+      </c>
+      <c r="G191" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vwo5H1UfscU | Short: https://www.youtube.com/watch?v=Muie07S9UA8</v>
       </c>
       <c r="I191" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1173,7 +1173,13 @@
         <v>cripto rendimento fixo</v>
       </c>
       <c r="D42" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F42" s="1" t="str">
+        <v>09/09/2026</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=yiT_-alVCho | Short: https://www.youtube.com/watch?v=z8qLkhL9Clo</v>
       </c>
       <c r="I42" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2754,7 +2754,13 @@
         <v>seguro embutido credito</v>
       </c>
       <c r="D129" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F129" s="1" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="G129" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Mg73-YsYvwc | Short: https://www.youtube.com/watch?v=VseI9XVvbQg</v>
       </c>
       <c r="I129" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4984,7 +4984,13 @@
         <v>produtos ativos cpf</v>
       </c>
       <c r="D251" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F251" s="1" t="str">
+        <v>11/09/2026</v>
+      </c>
+      <c r="G251" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=hlOKWqoiW8Q | Short: https://www.youtube.com/watch?v=yWyMz82POvg</v>
       </c>
       <c r="I251" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5513,7 +5513,13 @@
         <v>renegociacao ruim</v>
       </c>
       <c r="D280" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F280" s="1" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="G280" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=9QwEo_pzpKM | Short: https://www.youtube.com/watch?v=oheBQ0DoBBE</v>
       </c>
       <c r="I280" s="1" t="str">
         <v>Pirita</v>
